--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -1,56 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="132" windowWidth="14808" windowHeight="7980"/>
+    <workbookView xWindow="240" yWindow="140" windowWidth="14810" windowHeight="7980"/>
   </bookViews>
   <sheets>
-    <sheet name="产品登记编码管理导入导出新模板" sheetId="2" r:id="rId1"/>
+    <sheet name="产品登记编码管理导入导出模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品登记编码管理导入导出新模板!$1:$1</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>产品登记编码生成日</t>
+    <t>产品登记编码*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>产品状态</t>
+    <t>起息日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标客户类型</t>
+    <t>到期日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>产品运作模式</t>
-  </si>
-  <si>
-    <t>理财产品代码</t>
-  </si>
-  <si>
-    <t>行内标识码</t>
-  </si>
-  <si>
-    <t>产品登记编码</t>
+    <t>产品代码*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>产品名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>发行机构名称</t>
+    <t>产品运作模式*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,6 +60,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -75,22 +70,11 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -102,7 +86,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="44"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -131,32 +115,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1"/>
-    <cellStyle name="常规 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -172,7 +158,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -214,7 +200,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -249,7 +235,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -458,63 +444,292 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="21.08984375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>8</v>
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>7</v>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>6</v>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576">
+      <formula1>"01 封闭式净值型,02 封闭式非净值型,03 开放式净值型,04 开放式非净值型"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="132" windowWidth="14808" windowHeight="7980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16185" windowHeight="4995"/>
   </bookViews>
   <sheets>
     <sheet name="产品登记编码管理导入导出新模板" sheetId="2" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品登记编码管理导入导出新模板!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 
@@ -172,7 +173,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -214,7 +215,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -249,7 +250,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -459,21 +460,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -502,7 +504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -13,7 +13,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品登记编码管理导入导出新模板!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
@@ -141,17 +140,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -459,61 +464,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.625" style="5" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16185" windowHeight="4995"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16190" windowHeight="5000"/>
   </bookViews>
   <sheets>
     <sheet name="产品登记编码管理导入导出新模板" sheetId="2" r:id="rId1"/>
@@ -140,7 +140,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -153,9 +153,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -464,23 +461,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.625" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="14.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -508,9 +504,8 @@
       <c r="I1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16190" windowHeight="5000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16185" windowHeight="4995"/>
   </bookViews>
   <sheets>
     <sheet name="产品登记编码管理导入导出新模板" sheetId="2" r:id="rId1"/>
@@ -28,29 +28,30 @@
     <t>目标客户类型</t>
   </si>
   <si>
+    <t>理财产品代码</t>
+  </si>
+  <si>
+    <t>行内标识码</t>
+  </si>
+  <si>
+    <t>产品登记编码</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>发行机构名称</t>
+  </si>
+  <si>
     <t>产品运作模式</t>
-  </si>
-  <si>
-    <t>理财产品代码</t>
-  </si>
-  <si>
-    <t>行内标识码</t>
-  </si>
-  <si>
-    <t>产品登记编码</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>发行机构名称</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +91,11 @@
       <color indexed="8"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -140,7 +146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -154,6 +160,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -175,7 +184,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -217,7 +226,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -252,7 +261,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -462,38 +471,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.75" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -505,20 +514,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
+      <formula1>"01 封闭式净值型,02 封闭式非净值型,03 开放式净值型,04 开放式非净值型"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16190" windowHeight="5000"/>
+    <workbookView windowWidth="18840" windowHeight="4380"/>
   </bookViews>
   <sheets>
     <sheet name="产品登记编码管理导入导出新模板" sheetId="2" r:id="rId1"/>
@@ -12,66 +12,58 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品登记编码管理导入导出新模板!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>产品登记编码生成日</t>
+    <t>产品代码</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>产品登记编码</t>
+  </si>
+  <si>
+    <t>产品运作模式</t>
+  </si>
+  <si>
+    <t>目标客户类型</t>
   </si>
   <si>
     <t>产品状态</t>
   </si>
   <si>
-    <t>目标客户类型</t>
-  </si>
-  <si>
-    <t>产品运作模式</t>
-  </si>
-  <si>
-    <t>理财产品代码</t>
-  </si>
-  <si>
-    <t>行内标识码</t>
-  </si>
-  <si>
-    <t>产品登记编码</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>发行机构名称</t>
+    <t>产品登记编码生成日</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -82,18 +74,168 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -106,8 +248,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -117,58 +445,344 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
-    <cellStyle name="常规 3" xfId="2"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 3" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -217,7 +831,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -252,7 +866,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -455,70 +1069,60 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="14.0916666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.725" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.9083333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.3666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.6333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.3666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.725" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>7</v>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+    <row r="2" customHeight="1" spans="1:7">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18840" windowHeight="4380"/>
+    <workbookView windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="产品登记编码管理导入导出新模板" sheetId="2" r:id="rId1"/>
@@ -17,15 +17,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>产品代码</t>
+    <t>发行机构名称</t>
   </si>
   <si>
     <t>产品名称</t>
   </si>
   <si>
     <t>产品登记编码</t>
+  </si>
+  <si>
+    <t>行内标识码</t>
+  </si>
+  <si>
+    <t>理财产品代码</t>
   </si>
   <si>
     <t>产品运作模式</t>
@@ -45,12 +51,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +84,21 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -96,33 +117,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -143,14 +150,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -159,24 +158,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,6 +183,36 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -200,38 +221,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -250,43 +242,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -298,19 +386,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -322,115 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,24 +451,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -496,37 +470,27 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -548,162 +512,190 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1075,20 +1067,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.0916666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="23.725" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.9083333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.3666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.6333333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.3666666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.725" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="3" max="5" width="17.9083333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.3666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.6333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.3666666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20.725" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1110,8 +1102,14 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:7">
+    <row r="2" customHeight="1" spans="1:9">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1119,6 +1117,8 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
